--- a/IngSoftware/propuesta/CasosDeTests/Casos de Test - Modificacion - Gestionar Producto.xlsx
+++ b/IngSoftware/propuesta/CasosDeTests/Casos de Test - Modificacion - Gestionar Producto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\source\TrabajoFinalAus\IngSoftware\propuesta\CasosDeTests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D5F3B6-19AF-4084-B816-2E3D2D1F11C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC025823-E722-442E-9D29-01ED8B9C5027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="5" xr2:uid="{B0B4911A-AFEF-499F-AAD3-44A4176D5575}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B0B4911A-AFEF-499F-AAD3-44A4176D5575}"/>
   </bookViews>
   <sheets>
     <sheet name="3A-MODIFICACION" sheetId="8" r:id="rId1"/>
@@ -19,6 +19,9 @@
     <sheet name="3D-MODIFICACION, CATEGORIA" sheetId="13" r:id="rId4"/>
     <sheet name="3E-MODIFICACION, CANTIDAD NEGAT" sheetId="14" r:id="rId5"/>
     <sheet name="3F-MODIFICACION, CANTIDAD" sheetId="16" r:id="rId6"/>
+    <sheet name="3A1-BAJA" sheetId="17" r:id="rId7"/>
+    <sheet name="3A2-BAJA, CANCELAR" sheetId="18" r:id="rId8"/>
+    <sheet name="3F-MODIFICACION, DESCRIPCION" sheetId="19" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
   <si>
     <t>Prerequisitos</t>
   </si>
@@ -149,10 +152,6 @@
     <t>"5"</t>
   </si>
   <si>
-    <t>* Existe al menos un Producto con nombre "Torta de Chocolate" tal que este habilitado y sus cantidades sean tratadas como enteros.
-* Existe al menos una Categoria con nombre "Pastel"</t>
-  </si>
-  <si>
     <t>El Producto se modifica</t>
   </si>
   <si>
@@ -198,21 +197,7 @@
     <t>El Sistema mantiene seleccionado el nombre del producto pero NO actualiza el valor con la entrada.</t>
   </si>
   <si>
-    <t>El Sistema muestra el formulario de Modificacion de Producto con los siguientes campos:
-- Nombre (Este no se puede modificar).
-- Descripción.
-- Cantidad.
-- Categoría.
-- Unidad.
-- Habilitado.
-Y una leyenda indicando que se está realizando la Modificacion de un Producto junto al nombre del producto.</t>
-  </si>
-  <si>
     <t>3D</t>
-  </si>
-  <si>
-    <t>* Existe al menos un Producto con nombre "Torta de Chocolate" tal que este habilitado y sus cantidades sean tratadas como enteros.
-* NO Existen categorias habilitadas</t>
   </si>
   <si>
     <t>a</t>
@@ -257,6 +242,28 @@
 Y una leyenda indicando que se está realizando la Modificacion de un Producto junto al nombre del producto.</t>
   </si>
   <si>
+    <t>Modificacion de Producto, cantidades con mal formato.</t>
+  </si>
+  <si>
+    <t>Se selecciona la cantidad y se ingresa un valor entero.</t>
+  </si>
+  <si>
+    <t>Se selecciona la cantidad y se ingresa un valor erroneo.</t>
+  </si>
+  <si>
+    <t>"33.3.3"</t>
+  </si>
+  <si>
+    <t>El Sistema indica que la cantidad no tiene el formato que corresponde a un entero a un decimal y se deshabilita el boton de guardado. El Sistema permite realizar modificaciones en el formulario o cancelarlo.</t>
+  </si>
+  <si>
+    <t>El Producto no se modifica.</t>
+  </si>
+  <si>
+    <t>* Existe al menos un Producto con nombre "Torta de Chocolate" tal que este habilitado y sus cantidades sean tratadas como enteros.
+* Existe al menos una Categoria final habilitada, con nombre "Pastel".</t>
+  </si>
+  <si>
     <t>El Sistema muestra el formulario de Modificacion de Producto con los siguientes campos ya completos del producto:
 - Nombre (Este no se puede modificar).
 - Descripción.
@@ -264,23 +271,88 @@
 - Categoría.
 - Habilitado.
 Y una leyenda indicando que se está realizando la Modificacion de un Producto junto al nombre del producto.
-El Sistema deshabilita el boton de guardado con una leyenda indicando que se deben dar de alta/habilitar categorias.
+El Sistema deshabilita el boton de guardado con una leyenda indicando que se deben dar de alta/habilitar Categorias finales.
 El listado de Categorias se presenta vacio.</t>
   </si>
   <si>
-    <t>Modificacion de Producto, cantidades con mal formato.</t>
-  </si>
-  <si>
-    <t>Se selecciona la cantidad y se ingresa un valor entero.</t>
-  </si>
-  <si>
-    <t>Se selecciona la cantidad y se ingresa un valor erroneo.</t>
-  </si>
-  <si>
-    <t>"33.3.3"</t>
-  </si>
-  <si>
-    <t>El Sistema indica que la cantidad no tiene el formato que corresponde a un entero a un decimal y se deshabilita el boton de guardado. El Sistema permite realizar modificaciones en el formulario o cancelarlo.</t>
+    <t>* Existe al menos un Producto con nombre "Torta de Chocolate" tal que este habilitado y sus cantidades sean tratadas como enteros.
+* NO Existen categorias finales habilitadas dadas de alta.</t>
+  </si>
+  <si>
+    <t>Pasos de ejecucion</t>
+  </si>
+  <si>
+    <t>El Sistema cierra el aviso y procede a mostrar el Listado de Productos actualizado .</t>
+  </si>
+  <si>
+    <t>El Sistema da un aviso de que el producto sera deshabilitado y si se desea proceder con dos botones 'Aceptar' y 'Cancelar'.</t>
+  </si>
+  <si>
+    <t>El Sistema actualiza visualmente la opcion de habilitado.</t>
+  </si>
+  <si>
+    <t>Se deshabilita el producto deseleccionando la opcion "Habilitado"</t>
+  </si>
+  <si>
+    <t>El Sistema muestra el formulario de Modificacion de Producto con los siguientes campos:
+- Nombre (Este no se puede modificar).
+- Descripción.
+- Cantidad.
+- Categoría.
+- Habilitado.
+Y una leyenda indicando que se está realizando la Modificacion de un Producto junto al nombre del producto.</t>
+  </si>
+  <si>
+    <t>El Producto se da de baja</t>
+  </si>
+  <si>
+    <t>* Existe al menos un Producto con nombre "Torta de Chocolate"</t>
+  </si>
+  <si>
+    <t>Baja Producto, Caso Feliz</t>
+  </si>
+  <si>
+    <t>El Sistema cierra el aviso y permite modificar los datos.</t>
+  </si>
+  <si>
+    <t>Baja Producto, Cancelar confirmacion</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>3A1</t>
+  </si>
+  <si>
+    <t>Se selecciona el Producto y se selecciona la opcion 'Modificar Producto'</t>
+  </si>
+  <si>
+    <t>Se utiliza la opcion 'Guardar Producto'</t>
+  </si>
+  <si>
+    <t>El Sistema da un aviso de que el producto sera deshabilitado y si se desea proceder.</t>
+  </si>
+  <si>
+    <t>Se selecciona la opcion de continuar.</t>
+  </si>
+  <si>
+    <t>Se selecciona la opcion de cancelar.</t>
+  </si>
+  <si>
+    <t>Se selecciona la Descripcion de Producto.</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>El Sistema muestra el formulario de Modificacion de Producto con los siguientes campos:
+- Nombre (Este no se puede modificar).
+- Descripción.
+- Cantidad.
+- Categoría.
+- Unidad (Esta no se puede modificar).
+- Habilitado.
+Y una leyenda indicando que se está realizando la Modificacion de un Producto junto al nombre del producto.</t>
   </si>
 </sst>
 </file>
@@ -322,7 +394,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -470,11 +542,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -511,6 +596,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -566,14 +654,35 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="72">
+  <dxfs count="109">
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -1237,29 +1346,554 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1638,96 +2272,145 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{DA2E5B6E-5A86-4C1A-A795-D5BABE9FC70A}" name="Table2456" displayName="Table2456" ref="A7:G15" totalsRowShown="0" headerRowDxfId="71" dataDxfId="69" headerRowBorderDxfId="70" tableBorderDxfId="68" totalsRowBorderDxfId="67">
-  <autoFilter ref="A7:G15" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{CE06EC5D-F35A-4228-9B63-665F330CBC4F}" name="Numero de Paso" dataDxfId="66"/>
-    <tableColumn id="2" xr3:uid="{9F9A841B-05A8-4EDA-8B3E-536DBF4CAD10}" name="Accion" dataDxfId="65"/>
-    <tableColumn id="3" xr3:uid="{62CF6097-1D7B-4935-8441-328BA18440B7}" name="Entrada" dataDxfId="64"/>
-    <tableColumn id="4" xr3:uid="{AAAC5DAE-9097-4F23-9E7E-5B1E37BE7149}" name="Salida Esperada" dataDxfId="63"/>
-    <tableColumn id="5" xr3:uid="{9AD37DA1-0B6B-44A5-BC5B-FCA58F076A0F}" name="Salida Actual" dataDxfId="62"/>
-    <tableColumn id="6" xr3:uid="{B22CCC43-F5E1-488E-B945-87D9066602BF}" name="Resultados" dataDxfId="61"/>
-    <tableColumn id="7" xr3:uid="{706C642C-1763-4186-B9F3-AD188064B807}" name="Comentarios" dataDxfId="60"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{DA2E5B6E-5A86-4C1A-A795-D5BABE9FC70A}" name="Table2456" displayName="Table2456" ref="A7:H15" totalsRowShown="0" headerRowDxfId="96" dataDxfId="94" headerRowBorderDxfId="95" tableBorderDxfId="93" totalsRowBorderDxfId="92">
+  <autoFilter ref="A7:H15" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{CE06EC5D-F35A-4228-9B63-665F330CBC4F}" name="Numero de Paso" dataDxfId="91"/>
+    <tableColumn id="2" xr3:uid="{9F9A841B-05A8-4EDA-8B3E-536DBF4CAD10}" name="Accion" dataDxfId="90"/>
+    <tableColumn id="3" xr3:uid="{62CF6097-1D7B-4935-8441-328BA18440B7}" name="Entrada" dataDxfId="89"/>
+    <tableColumn id="4" xr3:uid="{AAAC5DAE-9097-4F23-9E7E-5B1E37BE7149}" name="Salida Esperada" dataDxfId="88"/>
+    <tableColumn id="5" xr3:uid="{9AD37DA1-0B6B-44A5-BC5B-FCA58F076A0F}" name="Salida Actual" dataDxfId="87"/>
+    <tableColumn id="6" xr3:uid="{B22CCC43-F5E1-488E-B945-87D9066602BF}" name="Resultados" dataDxfId="86"/>
+    <tableColumn id="7" xr3:uid="{706C642C-1763-4186-B9F3-AD188064B807}" name="Comentarios" dataDxfId="85"/>
+    <tableColumn id="8" xr3:uid="{3EDCDFBB-CF61-4056-8FE9-7B0A5C8C175C}" name="Column1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B7DCEE83-4A87-486D-ACBB-BAC98E3317AD}" name="Table24567" displayName="Table24567" ref="A7:G13" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B7DCEE83-4A87-486D-ACBB-BAC98E3317AD}" name="Table24567" displayName="Table24567" ref="A7:G13" totalsRowShown="0" headerRowDxfId="84" dataDxfId="82" headerRowBorderDxfId="83" tableBorderDxfId="81" totalsRowBorderDxfId="80">
   <autoFilter ref="A7:G13" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{E4847665-E7BD-4389-B7F2-D5CEA5F9CA09}" name="Numero de Paso" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{4B401B0F-A131-46C4-9646-9A22F27BAAA8}" name="Accion" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{F4ABD617-B2E3-464D-A4B9-42257B34D849}" name="Entrada" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{4A827BBB-9CCE-4F81-9339-16AE2622E16E}" name="Salida Esperada" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{C3809D33-CD56-4A79-9208-08958EA89E23}" name="Salida Actual" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{FC112A60-1320-4E6F-A7E1-D71BCC2A28D7}" name="Resultados" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{5085F4F7-D8BD-43EF-9B85-E627033C9F50}" name="Comentarios" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{E4847665-E7BD-4389-B7F2-D5CEA5F9CA09}" name="Numero de Paso" dataDxfId="79"/>
+    <tableColumn id="2" xr3:uid="{4B401B0F-A131-46C4-9646-9A22F27BAAA8}" name="Accion" dataDxfId="78"/>
+    <tableColumn id="3" xr3:uid="{F4ABD617-B2E3-464D-A4B9-42257B34D849}" name="Entrada" dataDxfId="77"/>
+    <tableColumn id="4" xr3:uid="{4A827BBB-9CCE-4F81-9339-16AE2622E16E}" name="Salida Esperada" dataDxfId="76"/>
+    <tableColumn id="5" xr3:uid="{C3809D33-CD56-4A79-9208-08958EA89E23}" name="Salida Actual" dataDxfId="75"/>
+    <tableColumn id="6" xr3:uid="{FC112A60-1320-4E6F-A7E1-D71BCC2A28D7}" name="Resultados" dataDxfId="74"/>
+    <tableColumn id="7" xr3:uid="{5085F4F7-D8BD-43EF-9B85-E627033C9F50}" name="Comentarios" dataDxfId="73"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FB225A9F-DB77-4CC7-B8B7-38032E9E2C7D}" name="Table245672" displayName="Table245672" ref="A7:G12" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46" headerRowBorderDxfId="44" tableBorderDxfId="45" totalsRowBorderDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FB225A9F-DB77-4CC7-B8B7-38032E9E2C7D}" name="Table245672" displayName="Table245672" ref="A7:G12" totalsRowShown="0" headerRowDxfId="72" dataDxfId="70" headerRowBorderDxfId="71" tableBorderDxfId="69" totalsRowBorderDxfId="68">
   <autoFilter ref="A7:G12" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{7A37D853-A959-49A6-A76E-FF06AD82E493}" name="Numero de Paso" dataDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{FF56AEE6-7D17-42BD-9E67-ED3B44965C83}" name="Accion" dataDxfId="41"/>
-    <tableColumn id="3" xr3:uid="{F882F994-F675-4005-AF98-E02BAF1C80FE}" name="Entrada" dataDxfId="40"/>
-    <tableColumn id="4" xr3:uid="{B8574B03-F37F-447E-9578-6C032BE80B00}" name="Salida Esperada" dataDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{6AEF7631-75DA-4AA8-9795-3496A3B185C7}" name="Salida Actual" dataDxfId="38"/>
-    <tableColumn id="6" xr3:uid="{948A968E-277F-4314-8CE3-C88C9498E213}" name="Resultados" dataDxfId="37"/>
-    <tableColumn id="7" xr3:uid="{C70D45B7-003F-4291-9757-312BB166789F}" name="Comentarios" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{7A37D853-A959-49A6-A76E-FF06AD82E493}" name="Numero de Paso" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{FF56AEE6-7D17-42BD-9E67-ED3B44965C83}" name="Accion" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{F882F994-F675-4005-AF98-E02BAF1C80FE}" name="Entrada" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{B8574B03-F37F-447E-9578-6C032BE80B00}" name="Salida Esperada" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{6AEF7631-75DA-4AA8-9795-3496A3B185C7}" name="Salida Actual" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{948A968E-277F-4314-8CE3-C88C9498E213}" name="Resultados" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{C70D45B7-003F-4291-9757-312BB166789F}" name="Comentarios" dataDxfId="61"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E336A33F-DB11-473E-978B-34B10231E872}" name="Table2456723" displayName="Table2456723" ref="A7:G12" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34" headerRowBorderDxfId="32" tableBorderDxfId="33" totalsRowBorderDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E336A33F-DB11-473E-978B-34B10231E872}" name="Table2456723" displayName="Table2456723" ref="A7:G12" totalsRowShown="0" headerRowDxfId="60" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57" totalsRowBorderDxfId="56">
   <autoFilter ref="A7:G12" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{572B7DBB-6505-42B0-BBCC-53B85AA383DC}" name="Numero de Paso" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{2EDCADBE-E723-4E34-811C-8A5BC22BBF71}" name="Accion" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{898CFDD5-80C2-4CD5-82F8-BA67A1018F85}" name="Entrada" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{301FBF97-2931-4569-939A-E32C249D59A0}" name="Salida Esperada" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{11D3B325-8031-42F0-9A3E-9B6EBE585076}" name="Salida Actual" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{26FF1804-3ECE-4705-9934-5407B812C0A8}" name="Resultados" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{0AA68694-FC8B-47F3-856A-7154C71DDF5A}" name="Comentarios" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{572B7DBB-6505-42B0-BBCC-53B85AA383DC}" name="Numero de Paso" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{2EDCADBE-E723-4E34-811C-8A5BC22BBF71}" name="Accion" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{898CFDD5-80C2-4CD5-82F8-BA67A1018F85}" name="Entrada" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{301FBF97-2931-4569-939A-E32C249D59A0}" name="Salida Esperada" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{11D3B325-8031-42F0-9A3E-9B6EBE585076}" name="Salida Actual" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{26FF1804-3ECE-4705-9934-5407B812C0A8}" name="Resultados" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{0AA68694-FC8B-47F3-856A-7154C71DDF5A}" name="Comentarios" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{73591F51-EDA2-44D3-A613-F7CB1CC722EB}" name="Table2456724" displayName="Table2456724" ref="A7:G13" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" headerRowBorderDxfId="20" tableBorderDxfId="21" totalsRowBorderDxfId="19">
-  <autoFilter ref="A7:G13" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{73591F51-EDA2-44D3-A613-F7CB1CC722EB}" name="Table2456724" displayName="Table2456724" ref="A7:G12" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45" totalsRowBorderDxfId="44">
+  <autoFilter ref="A7:G12" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{37E6F135-BD57-4182-B44B-4732D6894335}" name="Numero de Paso" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{5B2DE5BC-7191-4EF0-8E16-674A14B951B4}" name="Accion" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{099D50E0-8BA5-4CB3-A252-BC7D0107A092}" name="Entrada" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{31CE555C-DFFF-47DC-B64E-ED365DBB6D43}" name="Salida Esperada" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{26A90D99-6DB7-4B95-B4D8-0528F5AF967F}" name="Salida Actual" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{A4FCF705-5DED-45F5-8034-D02E9CDD7471}" name="Resultados" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{298E1256-525D-43C3-A70E-B9FD3A52DC64}" name="Comentarios" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{37E6F135-BD57-4182-B44B-4732D6894335}" name="Numero de Paso" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{5B2DE5BC-7191-4EF0-8E16-674A14B951B4}" name="Accion" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{099D50E0-8BA5-4CB3-A252-BC7D0107A092}" name="Entrada" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{31CE555C-DFFF-47DC-B64E-ED365DBB6D43}" name="Salida Esperada" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{26A90D99-6DB7-4B95-B4D8-0528F5AF967F}" name="Salida Actual" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{A4FCF705-5DED-45F5-8034-D02E9CDD7471}" name="Resultados" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{298E1256-525D-43C3-A70E-B9FD3A52DC64}" name="Comentarios" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3A2C47E6-511E-4AA6-A908-6BF04E4AAA66}" name="Table24567245" displayName="Table24567245" ref="A7:G13" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3A2C47E6-511E-4AA6-A908-6BF04E4AAA66}" name="Table24567245" displayName="Table24567245" ref="A7:G13" totalsRowShown="0" headerRowDxfId="108" dataDxfId="106" headerRowBorderDxfId="107" tableBorderDxfId="105" totalsRowBorderDxfId="104">
   <autoFilter ref="A7:G13" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{720582A2-D7D7-407C-9C46-FBA119AECF04}" name="Numero de Paso" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{330DAE55-5108-42B3-90B0-6751B7B182B1}" name="Accion" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{159125AB-DE17-4F71-B113-C725096BD0EA}" name="Entrada" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{7C50114A-628C-42B6-8A94-0F349E53E65E}" name="Salida Esperada" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{E7993204-0CCD-41B0-8420-0FF9DB6E2730}" name="Salida Actual" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{D8225DA2-68EB-4407-A2BB-75EDC9D84474}" name="Resultados" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{52A0EBEE-AD7A-408C-B183-983006EC4D71}" name="Comentarios" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{720582A2-D7D7-407C-9C46-FBA119AECF04}" name="Numero de Paso" dataDxfId="103"/>
+    <tableColumn id="2" xr3:uid="{330DAE55-5108-42B3-90B0-6751B7B182B1}" name="Accion" dataDxfId="102"/>
+    <tableColumn id="3" xr3:uid="{159125AB-DE17-4F71-B113-C725096BD0EA}" name="Entrada" dataDxfId="101"/>
+    <tableColumn id="4" xr3:uid="{7C50114A-628C-42B6-8A94-0F349E53E65E}" name="Salida Esperada" dataDxfId="100"/>
+    <tableColumn id="5" xr3:uid="{E7993204-0CCD-41B0-8420-0FF9DB6E2730}" name="Salida Actual" dataDxfId="99"/>
+    <tableColumn id="6" xr3:uid="{D8225DA2-68EB-4407-A2BB-75EDC9D84474}" name="Resultados" dataDxfId="98"/>
+    <tableColumn id="7" xr3:uid="{52A0EBEE-AD7A-408C-B183-983006EC4D71}" name="Comentarios" dataDxfId="97"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{A0070F41-6AAC-4B51-8EBD-5BE641E570CC}" name="Table24" displayName="Table24" ref="A7:G14" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35" headerRowBorderDxfId="33" tableBorderDxfId="34" totalsRowBorderDxfId="32">
+  <autoFilter ref="A7:G14" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{73E9C46E-BBEB-4990-9A63-D75AD8A72CF5}" name="Numero de Paso" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{BCE7D1F8-5714-45FA-A11C-61BC64DF3C09}" name="Accion" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{A136FF62-5B73-4BBF-BC86-A54E10568A38}" name="Entrada" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{25073EE7-6214-4B91-90B9-4BDE69450B22}" name="Salida Esperada" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{BFF5426D-3531-4D56-A5D8-27730C1A8584}" name="Salida Actual" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{52D0C67D-5552-4179-B81A-259BE45EC01B}" name="Resultados" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{0D0014A6-368B-4BA8-8EBE-AA0C27BC8722}" name="Comentarios" dataDxfId="25"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0313CED6-17D0-40E4-AC53-A8FD7C09CE52}" name="Table245" displayName="Table245" ref="A7:G14" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23" headerRowBorderDxfId="21" tableBorderDxfId="22" totalsRowBorderDxfId="20">
+  <autoFilter ref="A7:G14" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{E2C2328E-9E69-4C13-AFE5-02712F253616}" name="Numero de Paso" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{90D22A43-8AE0-40D9-8E72-EE7BBC6ED812}" name="Accion" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{E5B634E7-1214-41C6-A9B4-6BD60CB6738A}" name="Entrada" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{5CFC17A5-16DE-48AA-AF13-5A0A36F4DB82}" name="Salida Esperada" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{9CDB65A1-08C3-4A69-A769-1D7C71A4789B}" name="Salida Actual" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{27FC889D-DC24-483D-872E-FE8433D077A1}" name="Resultados" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{51B07143-015C-4A5C-AB79-BEC31BFDC954}" name="Comentarios" dataDxfId="13"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{CFF32AA4-FB15-467D-80AC-7CDD0B9C6BEE}" name="Table2456724510" displayName="Table2456724510" ref="A7:G13" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+  <autoFilter ref="A7:G13" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{D935A9ED-D403-4F28-BBC8-FE9AB67D6539}" name="Numero de Paso" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{74F60ABF-B8E6-4E32-A504-AB7B4CD4C52C}" name="Accion" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{73BDCA9E-DF34-4D4C-BA11-156AFE274B4B}" name="Entrada" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{76BE5717-6D0D-46F5-BB3C-ECDB4CC24CF6}" name="Salida Esperada" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{8C449815-7948-448F-8BC7-241D9F6A1D94}" name="Salida Actual" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{2BDC8098-6F9C-4D0D-9EAA-98E126BC9066}" name="Resultados" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{54A26719-5544-4AFC-8C02-365A78A5B4A3}" name="Comentarios" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2050,7 +2733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0EFC3EE-FCBF-42D6-9C81-DA2DCFEA52DC}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" customWidth="1"/>
@@ -2062,89 +2745,89 @@
     <col min="7" max="7" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="29"/>
-    </row>
-    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30"/>
+    </row>
+    <row r="2" spans="1:8" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="17">
+      <c r="B2" s="32"/>
+      <c r="C2" s="18">
         <v>3</v>
       </c>
-      <c r="D2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="20"/>
-    </row>
-    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
+      <c r="F2" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="21"/>
+    </row>
+    <row r="3" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="19" t="s">
+      <c r="B3" s="17"/>
+      <c r="C3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="20"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="20"/>
-    </row>
-    <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="G3" s="21"/>
+    </row>
+    <row r="4" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="18"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="19"/>
       <c r="E4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="21" t="s">
+      <c r="F4" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="23"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="26"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="24"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="25"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -2166,8 +2849,11 @@
       <c r="G7" s="9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="H7" s="36" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -2183,8 +2869,11 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="H8" s="35" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -2200,8 +2889,9 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:7" ht="174" x14ac:dyDescent="0.35">
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" ht="174" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>3</v>
       </c>
@@ -2212,13 +2902,14 @@
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -2234,8 +2925,9 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -2251,8 +2943,9 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -2268,40 +2961,43 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="14">
         <v>7</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="12"/>
-    </row>
-    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="4"/>
+      <c r="H15" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2339,86 +3035,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="29"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="17">
+      <c r="B2" s="32"/>
+      <c r="C2" s="18">
         <v>3</v>
       </c>
-      <c r="D2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="20"/>
+      <c r="F2" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="20"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="21"/>
       <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="18"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="19"/>
       <c r="E4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="20"/>
+      <c r="F4" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="21"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="24"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="26"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
@@ -2488,7 +3184,7 @@
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -2499,13 +3195,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -2516,13 +3212,13 @@
         <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -2533,13 +3229,13 @@
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -2581,86 +3277,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="29"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="17">
+      <c r="B2" s="32"/>
+      <c r="C2" s="18">
         <v>3</v>
       </c>
-      <c r="D2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" s="20"/>
+      <c r="F2" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7" ht="37" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="18"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="19"/>
       <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="18"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="19"/>
       <c r="E4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="20"/>
+      <c r="F4" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="21"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="24"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="26"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
@@ -2730,7 +3426,7 @@
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -2741,30 +3437,30 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="D11" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="33">
+      <c r="A12" s="15">
         <v>5</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -2806,86 +3502,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="29"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="17">
+      <c r="B2" s="32"/>
+      <c r="C2" s="18">
         <v>3</v>
       </c>
-      <c r="D2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="21"/>
+    </row>
+    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="20"/>
-    </row>
-    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="20"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="18"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="19"/>
       <c r="E4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="20"/>
+      <c r="F4" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="21"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="23"/>
+      <c r="A5" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="24"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="26"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
@@ -2955,7 +3651,7 @@
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -2966,30 +3662,30 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="33">
+      <c r="A12" s="15">
         <v>5</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -3018,7 +3714,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C316CCF7-7658-4351-91F4-0A3DDC2BD748}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" customWidth="1"/>
@@ -3031,86 +3727,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="29"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="17">
+      <c r="B2" s="32"/>
+      <c r="C2" s="18">
         <v>3</v>
       </c>
-      <c r="D2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" s="20"/>
+      <c r="F2" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" s="20"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="21"/>
       <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="18"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="19"/>
       <c r="E4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="20"/>
+      <c r="F4" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="21"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="24"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="26"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
@@ -3174,13 +3870,13 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -3191,43 +3887,34 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="33">
+      <c r="A12" s="15">
         <v>5</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="33"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -3265,86 +3952,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="29"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="17">
+      <c r="B2" s="32"/>
+      <c r="C2" s="18">
         <v>3</v>
       </c>
-      <c r="D2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" s="20"/>
+      <c r="F2" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="20"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="21"/>
       <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="18"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="19"/>
       <c r="E4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="20"/>
+      <c r="F4" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="21"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="24"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="26"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
@@ -3414,7 +4101,7 @@
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -3425,37 +4112,773 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="33">
+      <c r="A12" s="15">
         <v>5</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="33"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A5:G6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{081913B7-D245-4D44-960E-7CBE6E15EAC2}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" customWidth="1"/>
+    <col min="4" max="4" width="38.08984375" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="18">
+        <v>3</v>
+      </c>
+      <c r="D2" s="19"/>
+      <c r="E2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="21"/>
+    </row>
+    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="21"/>
+      <c r="E3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="21"/>
+    </row>
+    <row r="4" spans="1:7" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="19"/>
+      <c r="E4" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="24"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="25"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>5</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>6</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="34"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A5:G6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA1DF701-C0EB-4654-81E3-253317E2DAC5}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" customWidth="1"/>
+    <col min="4" max="4" width="38.08984375" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="18">
+        <v>3</v>
+      </c>
+      <c r="D2" s="19"/>
+      <c r="E2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="21"/>
+    </row>
+    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="21"/>
+      <c r="E3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="21"/>
+    </row>
+    <row r="4" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="19"/>
+      <c r="E4" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="24"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="25"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>5</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>6</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="34"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A5:G6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1B59568-F9C9-4053-8A77-5F50737015BD}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" customWidth="1"/>
+    <col min="4" max="4" width="38.08984375" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="18">
+        <v>3</v>
+      </c>
+      <c r="D2" s="19"/>
+      <c r="E2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="21"/>
+    </row>
+    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="21"/>
+      <c r="E3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="21"/>
+    </row>
+    <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="19"/>
+      <c r="E4" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="24"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="25"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="15">
+        <v>5</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="15"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>

--- a/IngSoftware/propuesta/CasosDeTests/Casos de Test - Modificacion - Gestionar Producto.xlsx
+++ b/IngSoftware/propuesta/CasosDeTests/Casos de Test - Modificacion - Gestionar Producto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\source\TrabajoFinalAus\IngSoftware\propuesta\CasosDeTests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC025823-E722-442E-9D29-01ED8B9C5027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3EA88A-EAF8-4DDC-B8A3-E50E0FC80EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B0B4911A-AFEF-499F-AAD3-44A4176D5575}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="85">
   <si>
     <t>Prerequisitos</t>
   </si>
@@ -97,15 +97,9 @@
     <t>Se visualiza el listado de Productos con los siguientes atribtutos del mismo: Nombre, Descripción, Cantidad, Categoría, Unidad, Tratar Unidad Como Entero y Habilitado.</t>
   </si>
   <si>
-    <t>El Sistema indica visualmente que se seleccionó el campo de Nombre y toma la entrada.</t>
-  </si>
-  <si>
     <t>Pasos de Ejecución</t>
   </si>
   <si>
-    <t>El Sistema despliega una lista de Categorías que filtra mediante Nombre de Categoría, una vez que se selecciona, se esconde el listado.</t>
-  </si>
-  <si>
     <t>ALTA</t>
   </si>
   <si>
@@ -127,34 +121,9 @@
     <t>Se selecciona el Producto y se utiliza el boton 'Modificar Producto'</t>
   </si>
   <si>
-    <t>Modificacion de Producto, caso feliz</t>
-  </si>
-  <si>
-    <t>Se selecciona la Descripcion del Producto y se modifica</t>
-  </si>
-  <si>
-    <t>Se selecciona la Cantidad del Producto.</t>
-  </si>
-  <si>
     <t>"Torta de Chocolate estilo Matilda"</t>
   </si>
   <si>
-    <t>El Sistema actualiza visualmente la opcion  incluyendo la nueva entrada.</t>
-  </si>
-  <si>
-    <t>Se se selecciona la opción de Categoría, se despliega un listado de todas las categorias.
-Se utiliza el filtro de Nombre y se selecciona la Categoría.</t>
-  </si>
-  <si>
-    <t>"Pastel"</t>
-  </si>
-  <si>
-    <t>"5"</t>
-  </si>
-  <si>
-    <t>El Producto se modifica</t>
-  </si>
-  <si>
     <t>Se selecciona la opcion de 'Guardar'.</t>
   </si>
   <si>
@@ -170,9 +139,6 @@
     <t>Modificacion de Producto, modificacion de nombre.</t>
   </si>
   <si>
-    <t>3A</t>
-  </si>
-  <si>
     <t>3B</t>
   </si>
   <si>
@@ -198,9 +164,6 @@
   </si>
   <si>
     <t>3D</t>
-  </si>
-  <si>
-    <t>a</t>
   </si>
   <si>
     <t>Modificacion de Producto, faltan categorias.</t>
@@ -342,17 +305,30 @@
     <t>Se selecciona la Descripcion de Producto.</t>
   </si>
   <si>
-    <t>Column1</t>
-  </si>
-  <si>
-    <t>El Sistema muestra el formulario de Modificacion de Producto con los siguientes campos:
-- Nombre (Este no se puede modificar).
-- Descripción.
-- Cantidad.
-- Categoría.
-- Unidad (Esta no se puede modificar).
-- Habilitado.
-Y una leyenda indicando que se está realizando la Modificacion de un Producto junto al nombre del producto.</t>
+    <t xml:space="preserve">MISSTORTAS </t>
+  </si>
+  <si>
+    <t>1B</t>
+  </si>
+  <si>
+    <t>Alta Producto: Sin categorias cargadas.</t>
+  </si>
+  <si>
+    <t>* Existe al menos una Unidad con nombre "Unidad" que maneja las cantidades como enteros dada de alta.</t>
+  </si>
+  <si>
+    <t>El Producto no se da de alta.</t>
+  </si>
+  <si>
+    <t>Se completa el formulario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Nombre = "Torta de Chocolate"
+* Descripcion = "Torta de Chocolate tipo Matilda"
+* Cantidad = "1"
+* Unidad = "Unidad"
+* Categoria = N/A
+</t>
   </si>
 </sst>
 </file>
@@ -394,7 +370,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -542,24 +518,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -600,6 +563,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -654,35 +618,42 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="109">
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="106">
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -696,87 +667,39 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -791,8 +714,35 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -808,42 +758,227 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
           <color rgb="FF000000"/>
         </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <left style="thin">
           <color rgb="FF000000"/>
-        </bottom>
-      </border>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
+        <bottom style="thin">
           <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -996,204 +1131,29 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <left style="thin">
           <color rgb="FF000000"/>
-        </bottom>
-      </border>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
+        <bottom style="thin">
           <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2272,145 +2232,145 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{DA2E5B6E-5A86-4C1A-A795-D5BABE9FC70A}" name="Table2456" displayName="Table2456" ref="A7:H15" totalsRowShown="0" headerRowDxfId="96" dataDxfId="94" headerRowBorderDxfId="95" tableBorderDxfId="93" totalsRowBorderDxfId="92">
-  <autoFilter ref="A7:H15" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{CE06EC5D-F35A-4228-9B63-665F330CBC4F}" name="Numero de Paso" dataDxfId="91"/>
-    <tableColumn id="2" xr3:uid="{9F9A841B-05A8-4EDA-8B3E-536DBF4CAD10}" name="Accion" dataDxfId="90"/>
-    <tableColumn id="3" xr3:uid="{62CF6097-1D7B-4935-8441-328BA18440B7}" name="Entrada" dataDxfId="89"/>
-    <tableColumn id="4" xr3:uid="{AAAC5DAE-9097-4F23-9E7E-5B1E37BE7149}" name="Salida Esperada" dataDxfId="88"/>
-    <tableColumn id="5" xr3:uid="{9AD37DA1-0B6B-44A5-BC5B-FCA58F076A0F}" name="Salida Actual" dataDxfId="87"/>
-    <tableColumn id="6" xr3:uid="{B22CCC43-F5E1-488E-B945-87D9066602BF}" name="Resultados" dataDxfId="86"/>
-    <tableColumn id="7" xr3:uid="{706C642C-1763-4186-B9F3-AD188064B807}" name="Comentarios" dataDxfId="85"/>
-    <tableColumn id="8" xr3:uid="{3EDCDFBB-CF61-4056-8FE9-7B0A5C8C175C}" name="Column1" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{715B9BAD-1497-41F0-B764-45044D3C92AC}" name="Table23" displayName="Table23" ref="A7:E9" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+  <autoFilter ref="A7:E9" xr:uid="{715B9BAD-1497-41F0-B764-45044D3C92AC}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{A93CF38D-7DFE-4F9A-9377-898DFF943F87}" name="Numero de Paso" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{0702067E-FD3D-44DC-9E82-1D0504306ED4}" name="Accion" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{7C9F77C2-31E9-4117-A7A2-F7356C3FC7AE}" name="Entrada" dataDxfId="2">
+      <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
+- Cantidad = "1"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{7AD3CC43-D1D7-4195-9746-65A7A8FD220B}" name="Resultados" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{986A7CE9-EF2E-40D3-A217-09C2FB7B25F3}" name="Comentarios" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B7DCEE83-4A87-486D-ACBB-BAC98E3317AD}" name="Table24567" displayName="Table24567" ref="A7:G13" totalsRowShown="0" headerRowDxfId="84" dataDxfId="82" headerRowBorderDxfId="83" tableBorderDxfId="81" totalsRowBorderDxfId="80">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B7DCEE83-4A87-486D-ACBB-BAC98E3317AD}" name="Table24567" displayName="Table24567" ref="A7:G13" totalsRowShown="0" headerRowDxfId="105" dataDxfId="103" headerRowBorderDxfId="104" tableBorderDxfId="102" totalsRowBorderDxfId="101">
   <autoFilter ref="A7:G13" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{E4847665-E7BD-4389-B7F2-D5CEA5F9CA09}" name="Numero de Paso" dataDxfId="79"/>
-    <tableColumn id="2" xr3:uid="{4B401B0F-A131-46C4-9646-9A22F27BAAA8}" name="Accion" dataDxfId="78"/>
-    <tableColumn id="3" xr3:uid="{F4ABD617-B2E3-464D-A4B9-42257B34D849}" name="Entrada" dataDxfId="77"/>
-    <tableColumn id="4" xr3:uid="{4A827BBB-9CCE-4F81-9339-16AE2622E16E}" name="Salida Esperada" dataDxfId="76"/>
-    <tableColumn id="5" xr3:uid="{C3809D33-CD56-4A79-9208-08958EA89E23}" name="Salida Actual" dataDxfId="75"/>
-    <tableColumn id="6" xr3:uid="{FC112A60-1320-4E6F-A7E1-D71BCC2A28D7}" name="Resultados" dataDxfId="74"/>
-    <tableColumn id="7" xr3:uid="{5085F4F7-D8BD-43EF-9B85-E627033C9F50}" name="Comentarios" dataDxfId="73"/>
+    <tableColumn id="1" xr3:uid="{E4847665-E7BD-4389-B7F2-D5CEA5F9CA09}" name="Numero de Paso" dataDxfId="100"/>
+    <tableColumn id="2" xr3:uid="{4B401B0F-A131-46C4-9646-9A22F27BAAA8}" name="Accion" dataDxfId="99"/>
+    <tableColumn id="3" xr3:uid="{F4ABD617-B2E3-464D-A4B9-42257B34D849}" name="Entrada" dataDxfId="98"/>
+    <tableColumn id="4" xr3:uid="{4A827BBB-9CCE-4F81-9339-16AE2622E16E}" name="Salida Esperada" dataDxfId="97"/>
+    <tableColumn id="5" xr3:uid="{C3809D33-CD56-4A79-9208-08958EA89E23}" name="Salida Actual" dataDxfId="96"/>
+    <tableColumn id="6" xr3:uid="{FC112A60-1320-4E6F-A7E1-D71BCC2A28D7}" name="Resultados" dataDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{5085F4F7-D8BD-43EF-9B85-E627033C9F50}" name="Comentarios" dataDxfId="94"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FB225A9F-DB77-4CC7-B8B7-38032E9E2C7D}" name="Table245672" displayName="Table245672" ref="A7:G12" totalsRowShown="0" headerRowDxfId="72" dataDxfId="70" headerRowBorderDxfId="71" tableBorderDxfId="69" totalsRowBorderDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FB225A9F-DB77-4CC7-B8B7-38032E9E2C7D}" name="Table245672" displayName="Table245672" ref="A7:G12" totalsRowShown="0" headerRowDxfId="93" dataDxfId="91" headerRowBorderDxfId="92" tableBorderDxfId="90" totalsRowBorderDxfId="89">
   <autoFilter ref="A7:G12" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{7A37D853-A959-49A6-A76E-FF06AD82E493}" name="Numero de Paso" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{FF56AEE6-7D17-42BD-9E67-ED3B44965C83}" name="Accion" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{F882F994-F675-4005-AF98-E02BAF1C80FE}" name="Entrada" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{B8574B03-F37F-447E-9578-6C032BE80B00}" name="Salida Esperada" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{6AEF7631-75DA-4AA8-9795-3496A3B185C7}" name="Salida Actual" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{948A968E-277F-4314-8CE3-C88C9498E213}" name="Resultados" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{C70D45B7-003F-4291-9757-312BB166789F}" name="Comentarios" dataDxfId="61"/>
+    <tableColumn id="1" xr3:uid="{7A37D853-A959-49A6-A76E-FF06AD82E493}" name="Numero de Paso" dataDxfId="88"/>
+    <tableColumn id="2" xr3:uid="{FF56AEE6-7D17-42BD-9E67-ED3B44965C83}" name="Accion" dataDxfId="87"/>
+    <tableColumn id="3" xr3:uid="{F882F994-F675-4005-AF98-E02BAF1C80FE}" name="Entrada" dataDxfId="86"/>
+    <tableColumn id="4" xr3:uid="{B8574B03-F37F-447E-9578-6C032BE80B00}" name="Salida Esperada" dataDxfId="85"/>
+    <tableColumn id="5" xr3:uid="{6AEF7631-75DA-4AA8-9795-3496A3B185C7}" name="Salida Actual" dataDxfId="84"/>
+    <tableColumn id="6" xr3:uid="{948A968E-277F-4314-8CE3-C88C9498E213}" name="Resultados" dataDxfId="83"/>
+    <tableColumn id="7" xr3:uid="{C70D45B7-003F-4291-9757-312BB166789F}" name="Comentarios" dataDxfId="82"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E336A33F-DB11-473E-978B-34B10231E872}" name="Table2456723" displayName="Table2456723" ref="A7:G12" totalsRowShown="0" headerRowDxfId="60" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57" totalsRowBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E336A33F-DB11-473E-978B-34B10231E872}" name="Table2456723" displayName="Table2456723" ref="A7:G12" totalsRowShown="0" headerRowDxfId="81" dataDxfId="79" headerRowBorderDxfId="80" tableBorderDxfId="78" totalsRowBorderDxfId="77">
   <autoFilter ref="A7:G12" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{572B7DBB-6505-42B0-BBCC-53B85AA383DC}" name="Numero de Paso" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{2EDCADBE-E723-4E34-811C-8A5BC22BBF71}" name="Accion" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{898CFDD5-80C2-4CD5-82F8-BA67A1018F85}" name="Entrada" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{301FBF97-2931-4569-939A-E32C249D59A0}" name="Salida Esperada" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{11D3B325-8031-42F0-9A3E-9B6EBE585076}" name="Salida Actual" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{26FF1804-3ECE-4705-9934-5407B812C0A8}" name="Resultados" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{0AA68694-FC8B-47F3-856A-7154C71DDF5A}" name="Comentarios" dataDxfId="49"/>
+    <tableColumn id="1" xr3:uid="{572B7DBB-6505-42B0-BBCC-53B85AA383DC}" name="Numero de Paso" dataDxfId="76"/>
+    <tableColumn id="2" xr3:uid="{2EDCADBE-E723-4E34-811C-8A5BC22BBF71}" name="Accion" dataDxfId="75"/>
+    <tableColumn id="3" xr3:uid="{898CFDD5-80C2-4CD5-82F8-BA67A1018F85}" name="Entrada" dataDxfId="74"/>
+    <tableColumn id="4" xr3:uid="{301FBF97-2931-4569-939A-E32C249D59A0}" name="Salida Esperada" dataDxfId="73"/>
+    <tableColumn id="5" xr3:uid="{11D3B325-8031-42F0-9A3E-9B6EBE585076}" name="Salida Actual" dataDxfId="72"/>
+    <tableColumn id="6" xr3:uid="{26FF1804-3ECE-4705-9934-5407B812C0A8}" name="Resultados" dataDxfId="71"/>
+    <tableColumn id="7" xr3:uid="{0AA68694-FC8B-47F3-856A-7154C71DDF5A}" name="Comentarios" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{73591F51-EDA2-44D3-A613-F7CB1CC722EB}" name="Table2456724" displayName="Table2456724" ref="A7:G12" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45" totalsRowBorderDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{73591F51-EDA2-44D3-A613-F7CB1CC722EB}" name="Table2456724" displayName="Table2456724" ref="A7:G12" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68" tableBorderDxfId="66" totalsRowBorderDxfId="65">
   <autoFilter ref="A7:G12" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{37E6F135-BD57-4182-B44B-4732D6894335}" name="Numero de Paso" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{5B2DE5BC-7191-4EF0-8E16-674A14B951B4}" name="Accion" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{099D50E0-8BA5-4CB3-A252-BC7D0107A092}" name="Entrada" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{31CE555C-DFFF-47DC-B64E-ED365DBB6D43}" name="Salida Esperada" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{26A90D99-6DB7-4B95-B4D8-0528F5AF967F}" name="Salida Actual" dataDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{A4FCF705-5DED-45F5-8034-D02E9CDD7471}" name="Resultados" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{298E1256-525D-43C3-A70E-B9FD3A52DC64}" name="Comentarios" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{37E6F135-BD57-4182-B44B-4732D6894335}" name="Numero de Paso" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{5B2DE5BC-7191-4EF0-8E16-674A14B951B4}" name="Accion" dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{099D50E0-8BA5-4CB3-A252-BC7D0107A092}" name="Entrada" dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{31CE555C-DFFF-47DC-B64E-ED365DBB6D43}" name="Salida Esperada" dataDxfId="61"/>
+    <tableColumn id="5" xr3:uid="{26A90D99-6DB7-4B95-B4D8-0528F5AF967F}" name="Salida Actual" dataDxfId="60"/>
+    <tableColumn id="6" xr3:uid="{A4FCF705-5DED-45F5-8034-D02E9CDD7471}" name="Resultados" dataDxfId="59"/>
+    <tableColumn id="7" xr3:uid="{298E1256-525D-43C3-A70E-B9FD3A52DC64}" name="Comentarios" dataDxfId="58"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3A2C47E6-511E-4AA6-A908-6BF04E4AAA66}" name="Table24567245" displayName="Table24567245" ref="A7:G13" totalsRowShown="0" headerRowDxfId="108" dataDxfId="106" headerRowBorderDxfId="107" tableBorderDxfId="105" totalsRowBorderDxfId="104">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3A2C47E6-511E-4AA6-A908-6BF04E4AAA66}" name="Table24567245" displayName="Table24567245" ref="A7:G13" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56" tableBorderDxfId="54" totalsRowBorderDxfId="53">
   <autoFilter ref="A7:G13" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{720582A2-D7D7-407C-9C46-FBA119AECF04}" name="Numero de Paso" dataDxfId="103"/>
-    <tableColumn id="2" xr3:uid="{330DAE55-5108-42B3-90B0-6751B7B182B1}" name="Accion" dataDxfId="102"/>
-    <tableColumn id="3" xr3:uid="{159125AB-DE17-4F71-B113-C725096BD0EA}" name="Entrada" dataDxfId="101"/>
-    <tableColumn id="4" xr3:uid="{7C50114A-628C-42B6-8A94-0F349E53E65E}" name="Salida Esperada" dataDxfId="100"/>
-    <tableColumn id="5" xr3:uid="{E7993204-0CCD-41B0-8420-0FF9DB6E2730}" name="Salida Actual" dataDxfId="99"/>
-    <tableColumn id="6" xr3:uid="{D8225DA2-68EB-4407-A2BB-75EDC9D84474}" name="Resultados" dataDxfId="98"/>
-    <tableColumn id="7" xr3:uid="{52A0EBEE-AD7A-408C-B183-983006EC4D71}" name="Comentarios" dataDxfId="97"/>
+    <tableColumn id="1" xr3:uid="{720582A2-D7D7-407C-9C46-FBA119AECF04}" name="Numero de Paso" dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{330DAE55-5108-42B3-90B0-6751B7B182B1}" name="Accion" dataDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{159125AB-DE17-4F71-B113-C725096BD0EA}" name="Entrada" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{7C50114A-628C-42B6-8A94-0F349E53E65E}" name="Salida Esperada" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{E7993204-0CCD-41B0-8420-0FF9DB6E2730}" name="Salida Actual" dataDxfId="48"/>
+    <tableColumn id="6" xr3:uid="{D8225DA2-68EB-4407-A2BB-75EDC9D84474}" name="Resultados" dataDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{52A0EBEE-AD7A-408C-B183-983006EC4D71}" name="Comentarios" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{A0070F41-6AAC-4B51-8EBD-5BE641E570CC}" name="Table24" displayName="Table24" ref="A7:G14" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35" headerRowBorderDxfId="33" tableBorderDxfId="34" totalsRowBorderDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{A0070F41-6AAC-4B51-8EBD-5BE641E570CC}" name="Table24" displayName="Table24" ref="A7:G14" totalsRowShown="0" headerRowDxfId="45" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="42" totalsRowBorderDxfId="41">
   <autoFilter ref="A7:G14" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{73E9C46E-BBEB-4990-9A63-D75AD8A72CF5}" name="Numero de Paso" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{BCE7D1F8-5714-45FA-A11C-61BC64DF3C09}" name="Accion" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{A136FF62-5B73-4BBF-BC86-A54E10568A38}" name="Entrada" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{25073EE7-6214-4B91-90B9-4BDE69450B22}" name="Salida Esperada" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{BFF5426D-3531-4D56-A5D8-27730C1A8584}" name="Salida Actual" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{52D0C67D-5552-4179-B81A-259BE45EC01B}" name="Resultados" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{0D0014A6-368B-4BA8-8EBE-AA0C27BC8722}" name="Comentarios" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{73E9C46E-BBEB-4990-9A63-D75AD8A72CF5}" name="Numero de Paso" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{BCE7D1F8-5714-45FA-A11C-61BC64DF3C09}" name="Accion" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{A136FF62-5B73-4BBF-BC86-A54E10568A38}" name="Entrada" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{25073EE7-6214-4B91-90B9-4BDE69450B22}" name="Salida Esperada" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{BFF5426D-3531-4D56-A5D8-27730C1A8584}" name="Salida Actual" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{52D0C67D-5552-4179-B81A-259BE45EC01B}" name="Resultados" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{0D0014A6-368B-4BA8-8EBE-AA0C27BC8722}" name="Comentarios" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0313CED6-17D0-40E4-AC53-A8FD7C09CE52}" name="Table245" displayName="Table245" ref="A7:G14" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23" headerRowBorderDxfId="21" tableBorderDxfId="22" totalsRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0313CED6-17D0-40E4-AC53-A8FD7C09CE52}" name="Table245" displayName="Table245" ref="A7:G14" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
   <autoFilter ref="A7:G14" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{E2C2328E-9E69-4C13-AFE5-02712F253616}" name="Numero de Paso" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{90D22A43-8AE0-40D9-8E72-EE7BBC6ED812}" name="Accion" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{E5B634E7-1214-41C6-A9B4-6BD60CB6738A}" name="Entrada" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{5CFC17A5-16DE-48AA-AF13-5A0A36F4DB82}" name="Salida Esperada" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{9CDB65A1-08C3-4A69-A769-1D7C71A4789B}" name="Salida Actual" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{27FC889D-DC24-483D-872E-FE8433D077A1}" name="Resultados" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{51B07143-015C-4A5C-AB79-BEC31BFDC954}" name="Comentarios" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{E2C2328E-9E69-4C13-AFE5-02712F253616}" name="Numero de Paso" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{90D22A43-8AE0-40D9-8E72-EE7BBC6ED812}" name="Accion" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{E5B634E7-1214-41C6-A9B4-6BD60CB6738A}" name="Entrada" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{5CFC17A5-16DE-48AA-AF13-5A0A36F4DB82}" name="Salida Esperada" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{9CDB65A1-08C3-4A69-A769-1D7C71A4789B}" name="Salida Actual" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{27FC889D-DC24-483D-872E-FE8433D077A1}" name="Resultados" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{51B07143-015C-4A5C-AB79-BEC31BFDC954}" name="Comentarios" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{CFF32AA4-FB15-467D-80AC-7CDD0B9C6BEE}" name="Table2456724510" displayName="Table2456724510" ref="A7:G13" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{CFF32AA4-FB15-467D-80AC-7CDD0B9C6BEE}" name="Table2456724510" displayName="Table2456724510" ref="A7:G13" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="17">
   <autoFilter ref="A7:G13" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{D935A9ED-D403-4F28-BBC8-FE9AB67D6539}" name="Numero de Paso" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{74F60ABF-B8E6-4E32-A504-AB7B4CD4C52C}" name="Accion" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{73BDCA9E-DF34-4D4C-BA11-156AFE274B4B}" name="Entrada" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{76BE5717-6D0D-46F5-BB3C-ECDB4CC24CF6}" name="Salida Esperada" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{8C449815-7948-448F-8BC7-241D9F6A1D94}" name="Salida Actual" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{2BDC8098-6F9C-4D0D-9EAA-98E126BC9066}" name="Resultados" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{54A26719-5544-4AFC-8C02-365A78A5B4A3}" name="Comentarios" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{D935A9ED-D403-4F28-BBC8-FE9AB67D6539}" name="Numero de Paso" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{74F60ABF-B8E6-4E32-A504-AB7B4CD4C52C}" name="Accion" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{73BDCA9E-DF34-4D4C-BA11-156AFE274B4B}" name="Entrada" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{76BE5717-6D0D-46F5-BB3C-ECDB4CC24CF6}" name="Salida Esperada" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{8C449815-7948-448F-8BC7-241D9F6A1D94}" name="Salida Actual" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{2BDC8098-6F9C-4D0D-9EAA-98E126BC9066}" name="Resultados" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{54A26719-5544-4AFC-8C02-365A78A5B4A3}" name="Comentarios" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2733,285 +2693,134 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0EFC3EE-FCBF-42D6-9C81-DA2DCFEA52DC}">
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" customWidth="1"/>
-    <col min="2" max="2" width="25.453125" customWidth="1"/>
-    <col min="3" max="3" width="19.81640625" customWidth="1"/>
-    <col min="4" max="4" width="38.08984375" customWidth="1"/>
-    <col min="5" max="5" width="19.54296875" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" customWidth="1"/>
-    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30"/>
-    </row>
-    <row r="2" spans="1:8" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31" t="s">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+    </row>
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="18">
-        <v>3</v>
-      </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="13" t="s">
+      <c r="B2" s="36"/>
+      <c r="C2" s="37">
+        <v>1</v>
+      </c>
+      <c r="D2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
+      <c r="E2" s="38" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="21"/>
-      <c r="E3" s="13" t="s">
+      <c r="B3" s="39"/>
+      <c r="C3" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="21"/>
-    </row>
-    <row r="4" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
+      <c r="E3" s="40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="13" t="s">
+      <c r="B4" s="39"/>
+      <c r="C4" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="24"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="25"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+      <c r="E4" s="37" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="41"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="7" t="s">
+      <c r="D7" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="E7" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="36" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
+    </row>
+    <row r="8" spans="1:5" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="45">
         <v>1</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A9" s="45">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="35" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
-        <v>2</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="D9" s="2"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" ht="174" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
-        <v>4</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" ht="87" x14ac:dyDescent="0.35">
-      <c r="A12" s="3">
-        <v>5</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="3">
-        <v>6</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="14">
-        <v>7</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="3">
-        <v>8</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="5">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A5:G6"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:G2"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -3023,100 +2832,100 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2817B42B-8EA3-4BEE-8161-E04A14F6342E}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" customWidth="1"/>
-    <col min="2" max="2" width="25.453125" customWidth="1"/>
-    <col min="3" max="3" width="19.81640625" customWidth="1"/>
-    <col min="4" max="4" width="38.08984375" customWidth="1"/>
-    <col min="5" max="5" width="19.54296875" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" customWidth="1"/>
-    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="38.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30"/>
-    </row>
-    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31" t="s">
+    <row r="1" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="31"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="18">
+      <c r="B2" s="33"/>
+      <c r="C2" s="19">
         <v>3</v>
       </c>
-      <c r="D2" s="19"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
+      <c r="F2" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="22"/>
+    </row>
+    <row r="3" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="21"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="22"/>
       <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="21"/>
-    </row>
-    <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
+      <c r="F3" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="22"/>
+    </row>
+    <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="20"/>
       <c r="E4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="24"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="25"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F4" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="22"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="26"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="28"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -3139,7 +2948,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -3156,86 +2965,86 @@
       <c r="F8" s="2"/>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="12"/>
     </row>
-    <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -3265,100 +3074,100 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66018BCA-3B7C-4AF8-8269-6EC25F810A64}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" customWidth="1"/>
-    <col min="2" max="2" width="25.453125" customWidth="1"/>
-    <col min="3" max="3" width="19.81640625" customWidth="1"/>
-    <col min="4" max="4" width="38.08984375" customWidth="1"/>
-    <col min="5" max="5" width="19.54296875" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" customWidth="1"/>
-    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="38.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30"/>
-    </row>
-    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31" t="s">
+    <row r="1" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="31"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="18">
+      <c r="B2" s="33"/>
+      <c r="C2" s="19">
         <v>3</v>
       </c>
-      <c r="D2" s="19"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="1:7" ht="37" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
+      <c r="F2" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="22"/>
+    </row>
+    <row r="3" spans="1:7" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="19"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="20"/>
       <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="21"/>
-    </row>
-    <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
+      <c r="F3" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="22"/>
+    </row>
+    <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="20"/>
       <c r="E4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="24"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="25"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F4" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="22"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="26"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="28"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -3381,7 +3190,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -3398,69 +3207,69 @@
       <c r="F8" s="2"/>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>5</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -3490,100 +3299,100 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A0AD40C-9C71-4E08-A211-7CBF3DB9CB35}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" customWidth="1"/>
-    <col min="2" max="2" width="25.453125" customWidth="1"/>
-    <col min="3" max="3" width="19.81640625" customWidth="1"/>
-    <col min="4" max="4" width="38.08984375" customWidth="1"/>
-    <col min="5" max="5" width="19.54296875" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" customWidth="1"/>
-    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="38.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30"/>
-    </row>
-    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31" t="s">
+    <row r="1" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="31"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="18">
+      <c r="B2" s="33"/>
+      <c r="C2" s="19">
         <v>3</v>
       </c>
-      <c r="D2" s="19"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
+      <c r="F2" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="22"/>
+    </row>
+    <row r="3" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="21"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="22"/>
       <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="21"/>
-    </row>
-    <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
+      <c r="F3" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="22"/>
+    </row>
+    <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="20"/>
       <c r="E4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="24"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="25"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F4" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="22"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="26"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="28"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -3606,7 +3415,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -3623,69 +3432,69 @@
       <c r="F8" s="2"/>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="270" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>5</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -3715,100 +3524,100 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C316CCF7-7658-4351-91F4-0A3DDC2BD748}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" customWidth="1"/>
-    <col min="2" max="2" width="25.453125" customWidth="1"/>
-    <col min="3" max="3" width="19.81640625" customWidth="1"/>
-    <col min="4" max="4" width="38.08984375" customWidth="1"/>
-    <col min="5" max="5" width="19.54296875" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" customWidth="1"/>
-    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="38.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30"/>
-    </row>
-    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31" t="s">
+    <row r="1" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="31"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="18">
+      <c r="B2" s="33"/>
+      <c r="C2" s="19">
         <v>3</v>
       </c>
-      <c r="D2" s="19"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
+      <c r="F2" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="22"/>
+    </row>
+    <row r="3" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="21"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="22"/>
       <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="21"/>
-    </row>
-    <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
+      <c r="F3" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="22"/>
+    </row>
+    <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="20"/>
       <c r="E4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="24"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="25"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F4" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="22"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="26"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="28"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -3831,7 +3640,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -3848,69 +3657,69 @@
       <c r="F8" s="2"/>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>5</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -3940,100 +3749,100 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{339BE8D0-EAB3-429C-8752-DDD40C6D835D}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" customWidth="1"/>
-    <col min="2" max="2" width="25.453125" customWidth="1"/>
-    <col min="3" max="3" width="19.81640625" customWidth="1"/>
-    <col min="4" max="4" width="38.08984375" customWidth="1"/>
-    <col min="5" max="5" width="19.54296875" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" customWidth="1"/>
-    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="38.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30"/>
-    </row>
-    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31" t="s">
+    <row r="1" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="31"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="18">
+      <c r="B2" s="33"/>
+      <c r="C2" s="19">
         <v>3</v>
       </c>
-      <c r="D2" s="19"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
+      <c r="F2" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="22"/>
+    </row>
+    <row r="3" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="21"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="22"/>
       <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="21"/>
-    </row>
-    <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
+      <c r="F3" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="22"/>
+    </row>
+    <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="20"/>
       <c r="E4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="24"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="25"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F4" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="22"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="26"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="28"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -4056,7 +3865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -4073,75 +3882,75 @@
       <c r="F8" s="2"/>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>5</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="15"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
@@ -4174,100 +3983,100 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{081913B7-D245-4D44-960E-7CBE6E15EAC2}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" customWidth="1"/>
-    <col min="2" max="2" width="25.453125" customWidth="1"/>
-    <col min="3" max="3" width="19.81640625" customWidth="1"/>
-    <col min="4" max="4" width="38.08984375" customWidth="1"/>
-    <col min="5" max="5" width="19.54296875" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" customWidth="1"/>
-    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="38.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30"/>
-    </row>
-    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31" t="s">
+    <row r="1" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="31"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="18">
+      <c r="B2" s="33"/>
+      <c r="C2" s="19">
         <v>3</v>
       </c>
-      <c r="D2" s="19"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
+      <c r="F2" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="22"/>
+    </row>
+    <row r="3" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" s="21"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="22"/>
       <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="21"/>
-    </row>
-    <row r="4" spans="1:7" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
+      <c r="F3" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="22"/>
+    </row>
+    <row r="4" spans="1:7" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="20"/>
       <c r="E4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="24"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="25"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F4" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="22"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="26"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="28"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -4290,7 +4099,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -4307,93 +4116,93 @@
       <c r="F8" s="2"/>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="165" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="34"/>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="16"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -4403,17 +4212,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A5:G6"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A5:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -4425,100 +4234,100 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA1DF701-C0EB-4654-81E3-253317E2DAC5}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" customWidth="1"/>
-    <col min="2" max="2" width="25.453125" customWidth="1"/>
-    <col min="3" max="3" width="19.81640625" customWidth="1"/>
-    <col min="4" max="4" width="38.08984375" customWidth="1"/>
-    <col min="5" max="5" width="19.54296875" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" customWidth="1"/>
-    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="38.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30"/>
-    </row>
-    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31" t="s">
+    <row r="1" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="31"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="18">
+      <c r="B2" s="33"/>
+      <c r="C2" s="19">
         <v>3</v>
       </c>
-      <c r="D2" s="19"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
+      <c r="F2" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="22"/>
+    </row>
+    <row r="3" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="21"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="22"/>
       <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="21"/>
-    </row>
-    <row r="4" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
+      <c r="F3" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="22"/>
+    </row>
+    <row r="4" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="20"/>
       <c r="E4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="24"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="25"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F4" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="22"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="26"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="28"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -4541,7 +4350,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -4558,93 +4367,93 @@
       <c r="F8" s="2"/>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="165" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="34"/>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="16"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -4676,100 +4485,100 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1B59568-F9C9-4053-8A77-5F50737015BD}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" customWidth="1"/>
-    <col min="2" max="2" width="25.453125" customWidth="1"/>
-    <col min="3" max="3" width="19.81640625" customWidth="1"/>
-    <col min="4" max="4" width="38.08984375" customWidth="1"/>
-    <col min="5" max="5" width="19.54296875" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" customWidth="1"/>
-    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="38.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30"/>
-    </row>
-    <row r="2" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31" t="s">
+    <row r="1" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="31"/>
+    </row>
+    <row r="2" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="18">
+      <c r="B2" s="33"/>
+      <c r="C2" s="19">
         <v>3</v>
       </c>
-      <c r="D2" s="19"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
+      <c r="F2" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="22"/>
+    </row>
+    <row r="3" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="21"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="22"/>
       <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="21"/>
-    </row>
-    <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
+      <c r="F3" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="22"/>
+    </row>
+    <row r="4" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="20"/>
       <c r="E4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="24"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="25"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F4" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="22"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="26"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="28"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -4792,7 +4601,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -4809,75 +4618,75 @@
       <c r="F8" s="2"/>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>5</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="15"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
